--- a/hira_material_automation/output/monthly/202601_202610__acl_interference_screw_absorbable__040012__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202610__acl_interference_screw_absorbable__040012__normalized.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-04T23:53:37</t>
+          <t>2026-10-14T23:47:10</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7cd75a286402e98d53a7e76c1b0f660389a153664f6524e589bab542dd875e1d</t>
+          <t>2caac82b17d03132a94cb28af14a8de1d74072984264e97c658522f81d71c904</t>
         </is>
       </c>
     </row>
